--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -692,15 +692,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B18"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="24" min="1" max="1"/>
     <col width="108" customWidth="1" style="24" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="25">
       <c r="B2" s="26" t="inlineStr">
         <is>
@@ -715,6 +716,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="24" customHeight="1" s="25">
       <c r="B5" s="28" t="inlineStr">
         <is>
@@ -764,6 +766,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="24" customHeight="1" s="25">
       <c r="B13" s="28" t="inlineStr">
         <is>
@@ -785,6 +788,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1" s="25">
       <c r="B17" s="28" t="inlineStr">
         <is>
@@ -799,10 +803,32 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -810,7 +836,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1820,9 +1846,9 @@
       <formula2>10</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1830,7 +1856,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1854,6 +1880,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="25">
       <c r="A4" s="33" t="inlineStr">
         <is>
@@ -2186,8 +2213,8 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B26:F26"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -513,6 +513,150 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Risk priority number, before and after the action</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>RPN now</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="C0392B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'FMEA'!$B$11:$B$36</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'FMEA'!$J$11:$J$36</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>RPN after</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3F8F5A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'FMEA'!$B$11:$B$36</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'FMEA'!$R$11:$R$36</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <overlap val="-10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="3"/>
+        <tickMarkSkip val="3"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>19</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -1849,6 +1993,7 @@
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1880,7 +2025,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="25">
       <c r="A4" s="33" t="inlineStr">
         <is>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -145,7 +145,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -192,6 +192,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF333C49"/>
         <bgColor rgb="FF1F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFAEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -273,7 +278,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -418,6 +423,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1159,76 +1170,76 @@
       </c>
     </row>
     <row r="11" ht="45.75" customHeight="1" s="25">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>Agent closes a billing ticket</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="50" t="inlineStr">
         <is>
           <t>Adjustment has not posted yet</t>
         </is>
       </c>
-      <c r="C11" s="39" t="inlineStr">
+      <c r="C11" s="50" t="inlineStr">
         <is>
           <t>Customer discovers it themselves and contacts us again</t>
         </is>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="E11" s="39" t="inlineStr">
+      <c r="E11" s="50" t="inlineStr">
         <is>
           <t>System closes the ticket before the posting webhook confirms</t>
         </is>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F11" s="50" t="n">
         <v>8</v>
       </c>
-      <c r="G11" s="39" t="inlineStr">
+      <c r="G11" s="50" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H11" s="39" t="inlineStr">
+      <c r="H11" s="50" t="inlineStr">
         <is>
           <t>Only detected if the customer complains again</t>
         </is>
       </c>
-      <c r="I11" s="39" t="n">
+      <c r="I11" s="50" t="n">
         <v>9</v>
       </c>
       <c r="J11" s="39">
         <f>IF(COUNT(D11,F11,I11)=3,D11*F11*I11,"")</f>
         <v/>
       </c>
-      <c r="K11" s="39" t="inlineStr">
+      <c r="K11" s="50" t="inlineStr">
         <is>
           <t>Block Resolved status until the posting webhook confirms</t>
         </is>
       </c>
-      <c r="L11" s="39" t="inlineStr">
+      <c r="L11" s="50" t="inlineStr">
         <is>
           <t>Billing Ops</t>
         </is>
       </c>
-      <c r="M11" s="39" t="inlineStr">
+      <c r="M11" s="50" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="N11" s="39" t="inlineStr">
+      <c r="N11" s="50" t="inlineStr">
         <is>
           <t>Deferred-close rule shipped</t>
         </is>
       </c>
-      <c r="O11" s="39" t="n">
+      <c r="O11" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="P11" s="39" t="n">
+      <c r="P11" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" s="39" t="n">
+      <c r="Q11" s="50" t="n">
         <v>3</v>
       </c>
       <c r="R11" s="39">
@@ -1237,130 +1248,390 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="25">
-      <c r="A12" s="40" t="n"/>
-      <c r="B12" s="40" t="n"/>
-      <c r="C12" s="40" t="n"/>
-      <c r="D12" s="40" t="n"/>
-      <c r="E12" s="40" t="n"/>
-      <c r="F12" s="40" t="n"/>
-      <c r="G12" s="40" t="n"/>
-      <c r="H12" s="40" t="n"/>
-      <c r="I12" s="40" t="n"/>
+      <c r="A12" s="51" t="inlineStr">
+        <is>
+          <t>Tier 1 tags the contact reason</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t>Wrong reason selected</t>
+        </is>
+      </c>
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>Routing sends it to the wrong queue; customer repeats themselves</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="51" t="inlineStr">
+        <is>
+          <t>40 codes in a flat list, no search</t>
+        </is>
+      </c>
+      <c r="F12" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" s="51" t="inlineStr">
+        <is>
+          <t>Annual training</t>
+        </is>
+      </c>
+      <c r="H12" s="51" t="inlineStr">
+        <is>
+          <t>QA audit catches it weeks later on 2% of contacts</t>
+        </is>
+      </c>
+      <c r="I12" s="51" t="n">
+        <v>8</v>
+      </c>
       <c r="J12" s="41">
         <f>IF(COUNT(D12,F12,I12)=3,D12*F12*I12,"")</f>
         <v/>
       </c>
-      <c r="K12" s="40" t="n"/>
-      <c r="L12" s="40" t="n"/>
-      <c r="M12" s="40" t="n"/>
-      <c r="N12" s="40" t="n"/>
-      <c r="O12" s="40" t="n"/>
-      <c r="P12" s="40" t="n"/>
-      <c r="Q12" s="40" t="n"/>
+      <c r="K12" s="51" t="inlineStr">
+        <is>
+          <t>Cut the list to 12 codes and predict from the first message</t>
+        </is>
+      </c>
+      <c r="L12" s="51" t="inlineStr">
+        <is>
+          <t>Support Ops</t>
+        </is>
+      </c>
+      <c r="M12" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N12" s="51" t="inlineStr">
+        <is>
+          <t>Code list redesigned, pending release</t>
+        </is>
+      </c>
+      <c r="O12" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="P12" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="51" t="n">
+        <v>4</v>
+      </c>
       <c r="R12" s="41">
         <f>IF(COUNT(O12,P12,Q12)=3,O12*P12*Q12,"")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="25">
-      <c r="A13" s="40" t="n"/>
-      <c r="B13" s="40" t="n"/>
-      <c r="C13" s="40" t="n"/>
-      <c r="D13" s="40" t="n"/>
-      <c r="E13" s="40" t="n"/>
-      <c r="F13" s="40" t="n"/>
-      <c r="G13" s="40" t="n"/>
-      <c r="H13" s="40" t="n"/>
-      <c r="I13" s="40" t="n"/>
+      <c r="A13" s="51" t="inlineStr">
+        <is>
+          <t>Billing Ops verifies evidence</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>Evidence missing, ticket bounced back</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>Adds a full day to the resolution</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="51" t="inlineStr">
+        <is>
+          <t>Tier 1 has no checklist for what Billing needs</t>
+        </is>
+      </c>
+      <c r="F13" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>Wiki page nobody opens</t>
+        </is>
+      </c>
+      <c r="H13" s="51" t="inlineStr">
+        <is>
+          <t>Detected immediately on bounce-back</t>
+        </is>
+      </c>
+      <c r="I13" s="51" t="n">
+        <v>3</v>
+      </c>
       <c r="J13" s="41">
         <f>IF(COUNT(D13,F13,I13)=3,D13*F13*I13,"")</f>
         <v/>
       </c>
-      <c r="K13" s="40" t="n"/>
-      <c r="L13" s="40" t="n"/>
-      <c r="M13" s="40" t="n"/>
-      <c r="N13" s="40" t="n"/>
-      <c r="O13" s="40" t="n"/>
-      <c r="P13" s="40" t="n"/>
-      <c r="Q13" s="40" t="n"/>
+      <c r="K13" s="51" t="inlineStr">
+        <is>
+          <t>Required-fields form before hand-off</t>
+        </is>
+      </c>
+      <c r="L13" s="51" t="inlineStr">
+        <is>
+          <t>Support Ops</t>
+        </is>
+      </c>
+      <c r="M13" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N13" s="51" t="inlineStr">
+        <is>
+          <t>Form live since August</t>
+        </is>
+      </c>
+      <c r="O13" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="51" t="n">
+        <v>3</v>
+      </c>
       <c r="R13" s="41">
         <f>IF(COUNT(O13,P13,Q13)=3,O13*P13*Q13,"")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="25">
-      <c r="A14" s="40" t="n"/>
-      <c r="B14" s="40" t="n"/>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="40" t="n"/>
-      <c r="E14" s="40" t="n"/>
-      <c r="F14" s="40" t="n"/>
-      <c r="G14" s="40" t="n"/>
-      <c r="H14" s="40" t="n"/>
-      <c r="I14" s="40" t="n"/>
+      <c r="A14" s="51" t="inlineStr">
+        <is>
+          <t>Nightly adjustment batch runs</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>Batch fails silently</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>Every adjustment that day is late; nobody knows until customers call</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" s="51" t="inlineStr">
+        <is>
+          <t>No alerting on batch exit code</t>
+        </is>
+      </c>
+      <c r="F14" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H14" s="51" t="inlineStr">
+        <is>
+          <t>Discovered next morning by chance</t>
+        </is>
+      </c>
+      <c r="I14" s="51" t="n">
+        <v>9</v>
+      </c>
       <c r="J14" s="41">
         <f>IF(COUNT(D14,F14,I14)=3,D14*F14*I14,"")</f>
         <v/>
       </c>
-      <c r="K14" s="40" t="n"/>
-      <c r="L14" s="40" t="n"/>
-      <c r="M14" s="40" t="n"/>
-      <c r="N14" s="40" t="n"/>
-      <c r="O14" s="40" t="n"/>
-      <c r="P14" s="40" t="n"/>
-      <c r="Q14" s="40" t="n"/>
+      <c r="K14" s="51" t="inlineStr">
+        <is>
+          <t>Alert on non-zero exit to the on-call channel</t>
+        </is>
+      </c>
+      <c r="L14" s="51" t="inlineStr">
+        <is>
+          <t>Platform Eng</t>
+        </is>
+      </c>
+      <c r="M14" s="51" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="N14" s="51" t="inlineStr">
+        <is>
+          <t>Alerting deployed</t>
+        </is>
+      </c>
+      <c r="O14" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="P14" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="51" t="n">
+        <v>2</v>
+      </c>
       <c r="R14" s="41">
         <f>IF(COUNT(O14,P14,Q14)=3,O14*P14*Q14,"")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="25">
-      <c r="A15" s="40" t="n"/>
-      <c r="B15" s="40" t="n"/>
-      <c r="C15" s="40" t="n"/>
-      <c r="D15" s="40" t="n"/>
-      <c r="E15" s="40" t="n"/>
-      <c r="F15" s="40" t="n"/>
-      <c r="G15" s="40" t="n"/>
-      <c r="H15" s="40" t="n"/>
-      <c r="I15" s="40" t="n"/>
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>Agent applies a goodwill credit</t>
+        </is>
+      </c>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t>Credit exceeds the agent's authority</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="inlineStr">
+        <is>
+          <t>Margin leakage; caught in month-end reconciliation</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="51" t="inlineStr">
+        <is>
+          <t>Limit is documented but not enforced in the tool</t>
+        </is>
+      </c>
+      <c r="F15" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="51" t="inlineStr">
+        <is>
+          <t>SOP states the limit</t>
+        </is>
+      </c>
+      <c r="H15" s="51" t="inlineStr">
+        <is>
+          <t>Month-end reconciliation, up to 30 days later</t>
+        </is>
+      </c>
+      <c r="I15" s="51" t="n">
+        <v>7</v>
+      </c>
       <c r="J15" s="41">
         <f>IF(COUNT(D15,F15,I15)=3,D15*F15*I15,"")</f>
         <v/>
       </c>
-      <c r="K15" s="40" t="n"/>
-      <c r="L15" s="40" t="n"/>
-      <c r="M15" s="40" t="n"/>
-      <c r="N15" s="40" t="n"/>
-      <c r="O15" s="40" t="n"/>
-      <c r="P15" s="40" t="n"/>
-      <c r="Q15" s="40" t="n"/>
+      <c r="K15" s="51" t="inlineStr">
+        <is>
+          <t>Enforce the limit in the credit form</t>
+        </is>
+      </c>
+      <c r="L15" s="51" t="inlineStr">
+        <is>
+          <t>Billing Ops</t>
+        </is>
+      </c>
+      <c r="M15" s="51" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="N15" s="51" t="inlineStr">
+        <is>
+          <t>In backlog</t>
+        </is>
+      </c>
+      <c r="O15" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" s="51" t="n">
+        <v>7</v>
+      </c>
       <c r="R15" s="41">
         <f>IF(COUNT(O15,P15,Q15)=3,O15*P15*Q15,"")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="25">
-      <c r="A16" s="40" t="n"/>
-      <c r="B16" s="40" t="n"/>
-      <c r="C16" s="40" t="n"/>
-      <c r="D16" s="40" t="n"/>
-      <c r="E16" s="40" t="n"/>
-      <c r="F16" s="40" t="n"/>
-      <c r="G16" s="40" t="n"/>
-      <c r="H16" s="40" t="n"/>
-      <c r="I16" s="40" t="n"/>
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>Customer confirms resolution</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>No confirmation ever arrives</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>Ticket auto-closes while the customer still has the problem</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="51" t="inlineStr">
+        <is>
+          <t>Auto-close at 96 hours with no reminder</t>
+        </is>
+      </c>
+      <c r="F16" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H16" s="51" t="inlineStr">
+        <is>
+          <t>Only visible as a reopen days later</t>
+        </is>
+      </c>
+      <c r="I16" s="51" t="n">
+        <v>8</v>
+      </c>
       <c r="J16" s="41">
         <f>IF(COUNT(D16,F16,I16)=3,D16*F16*I16,"")</f>
         <v/>
       </c>
-      <c r="K16" s="40" t="n"/>
-      <c r="L16" s="40" t="n"/>
-      <c r="M16" s="40" t="n"/>
-      <c r="N16" s="40" t="n"/>
-      <c r="O16" s="40" t="n"/>
-      <c r="P16" s="40" t="n"/>
-      <c r="Q16" s="40" t="n"/>
+      <c r="K16" s="51" t="inlineStr">
+        <is>
+          <t>Send a reminder at 48 hours before auto-close</t>
+        </is>
+      </c>
+      <c r="L16" s="51" t="inlineStr">
+        <is>
+          <t>Support Ops</t>
+        </is>
+      </c>
+      <c r="M16" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="N16" s="51" t="inlineStr">
+        <is>
+          <t>Reminder shipped</t>
+        </is>
+      </c>
+      <c r="O16" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="51" t="n">
+        <v>4</v>
+      </c>
       <c r="R16" s="41">
         <f>IF(COUNT(O16,P16,Q16)=3,O16*P16*Q16,"")</f>
         <v/>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -562,6 +562,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'FMEA'!$B$11:$B$36</f>
@@ -587,6 +588,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'FMEA'!$B$11:$B$36</f>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -144,8 +144,12 @@
       <color rgb="FF1F2937"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -197,6 +201,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFECFAEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -278,7 +287,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -429,6 +438,8 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,7 +549,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Risk priority number, before and after the action</a:t>
+              <a:t>Risk priority number — did the action actually reduce it?</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -605,6 +616,40 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Act above this (RPN 100)</v>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'FMEA'!$T$11:$T$36</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -635,7 +680,7 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -647,7 +692,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>19</col>
+      <col>21</col>
       <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
@@ -995,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="24" min="1" max="1"/>
@@ -1170,6 +1215,11 @@
           <t>New RPN</t>
         </is>
       </c>
+      <c r="T10" s="52" t="inlineStr">
+        <is>
+          <t>Act above</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="45.75" customHeight="1" s="25">
       <c r="A11" s="50" t="inlineStr">
@@ -1248,6 +1298,10 @@
         <f>IF(COUNT(O11,P11,Q11)=3,O11*P11*Q11,"")</f>
         <v/>
       </c>
+      <c r="T11" s="53">
+        <f>IF(J11="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="25">
       <c r="A12" s="51" t="inlineStr">
@@ -1326,6 +1380,10 @@
         <f>IF(COUNT(O12,P12,Q12)=3,O12*P12*Q12,"")</f>
         <v/>
       </c>
+      <c r="T12" s="53">
+        <f>IF(J12="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="25">
       <c r="A13" s="51" t="inlineStr">
@@ -1404,6 +1462,10 @@
         <f>IF(COUNT(O13,P13,Q13)=3,O13*P13*Q13,"")</f>
         <v/>
       </c>
+      <c r="T13" s="53">
+        <f>IF(J13="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="25">
       <c r="A14" s="51" t="inlineStr">
@@ -1482,6 +1544,10 @@
         <f>IF(COUNT(O14,P14,Q14)=3,O14*P14*Q14,"")</f>
         <v/>
       </c>
+      <c r="T14" s="53">
+        <f>IF(J14="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" s="25">
       <c r="A15" s="51" t="inlineStr">
@@ -1560,6 +1626,10 @@
         <f>IF(COUNT(O15,P15,Q15)=3,O15*P15*Q15,"")</f>
         <v/>
       </c>
+      <c r="T15" s="53">
+        <f>IF(J15="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="25">
       <c r="A16" s="51" t="inlineStr">
@@ -1636,6 +1706,10 @@
       </c>
       <c r="R16" s="41">
         <f>IF(COUNT(O16,P16,Q16)=3,O16*P16*Q16,"")</f>
+        <v/>
+      </c>
+      <c r="T16" s="53">
+        <f>IF(J16="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1664,6 +1738,10 @@
         <f>IF(COUNT(O17,P17,Q17)=3,O17*P17*Q17,"")</f>
         <v/>
       </c>
+      <c r="T17" s="53">
+        <f>IF(J17="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="25">
       <c r="A18" s="40" t="n"/>
@@ -1690,6 +1768,10 @@
         <f>IF(COUNT(O18,P18,Q18)=3,O18*P18*Q18,"")</f>
         <v/>
       </c>
+      <c r="T18" s="53">
+        <f>IF(J18="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="25">
       <c r="A19" s="40" t="n"/>
@@ -1716,6 +1798,10 @@
         <f>IF(COUNT(O19,P19,Q19)=3,O19*P19*Q19,"")</f>
         <v/>
       </c>
+      <c r="T19" s="53">
+        <f>IF(J19="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="25">
       <c r="A20" s="40" t="n"/>
@@ -1742,6 +1828,10 @@
         <f>IF(COUNT(O20,P20,Q20)=3,O20*P20*Q20,"")</f>
         <v/>
       </c>
+      <c r="T20" s="53">
+        <f>IF(J20="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="25">
       <c r="A21" s="40" t="n"/>
@@ -1768,6 +1858,10 @@
         <f>IF(COUNT(O21,P21,Q21)=3,O21*P21*Q21,"")</f>
         <v/>
       </c>
+      <c r="T21" s="53">
+        <f>IF(J21="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="25">
       <c r="A22" s="40" t="n"/>
@@ -1794,6 +1888,10 @@
         <f>IF(COUNT(O22,P22,Q22)=3,O22*P22*Q22,"")</f>
         <v/>
       </c>
+      <c r="T22" s="53">
+        <f>IF(J22="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="25">
       <c r="A23" s="40" t="n"/>
@@ -1820,6 +1918,10 @@
         <f>IF(COUNT(O23,P23,Q23)=3,O23*P23*Q23,"")</f>
         <v/>
       </c>
+      <c r="T23" s="53">
+        <f>IF(J23="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="25">
       <c r="A24" s="40" t="n"/>
@@ -1846,6 +1948,10 @@
         <f>IF(COUNT(O24,P24,Q24)=3,O24*P24*Q24,"")</f>
         <v/>
       </c>
+      <c r="T24" s="53">
+        <f>IF(J24="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="25">
       <c r="A25" s="40" t="n"/>
@@ -1872,6 +1978,10 @@
         <f>IF(COUNT(O25,P25,Q25)=3,O25*P25*Q25,"")</f>
         <v/>
       </c>
+      <c r="T25" s="53">
+        <f>IF(J25="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="25">
       <c r="A26" s="40" t="n"/>
@@ -1898,6 +2008,10 @@
         <f>IF(COUNT(O26,P26,Q26)=3,O26*P26*Q26,"")</f>
         <v/>
       </c>
+      <c r="T26" s="53">
+        <f>IF(J26="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="25">
       <c r="A27" s="40" t="n"/>
@@ -1924,6 +2038,10 @@
         <f>IF(COUNT(O27,P27,Q27)=3,O27*P27*Q27,"")</f>
         <v/>
       </c>
+      <c r="T27" s="53">
+        <f>IF(J27="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="25">
       <c r="A28" s="40" t="n"/>
@@ -1950,6 +2068,10 @@
         <f>IF(COUNT(O28,P28,Q28)=3,O28*P28*Q28,"")</f>
         <v/>
       </c>
+      <c r="T28" s="53">
+        <f>IF(J28="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="25">
       <c r="A29" s="40" t="n"/>
@@ -1976,6 +2098,10 @@
         <f>IF(COUNT(O29,P29,Q29)=3,O29*P29*Q29,"")</f>
         <v/>
       </c>
+      <c r="T29" s="53">
+        <f>IF(J29="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="25">
       <c r="A30" s="40" t="n"/>
@@ -2002,6 +2128,10 @@
         <f>IF(COUNT(O30,P30,Q30)=3,O30*P30*Q30,"")</f>
         <v/>
       </c>
+      <c r="T30" s="53">
+        <f>IF(J30="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="25">
       <c r="A31" s="40" t="n"/>
@@ -2028,6 +2158,10 @@
         <f>IF(COUNT(O31,P31,Q31)=3,O31*P31*Q31,"")</f>
         <v/>
       </c>
+      <c r="T31" s="53">
+        <f>IF(J31="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="25">
       <c r="A32" s="40" t="n"/>
@@ -2054,6 +2188,10 @@
         <f>IF(COUNT(O32,P32,Q32)=3,O32*P32*Q32,"")</f>
         <v/>
       </c>
+      <c r="T32" s="53">
+        <f>IF(J32="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="25">
       <c r="A33" s="40" t="n"/>
@@ -2080,6 +2218,10 @@
         <f>IF(COUNT(O33,P33,Q33)=3,O33*P33*Q33,"")</f>
         <v/>
       </c>
+      <c r="T33" s="53">
+        <f>IF(J33="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1" s="25">
       <c r="A34" s="40" t="n"/>
@@ -2106,6 +2248,10 @@
         <f>IF(COUNT(O34,P34,Q34)=3,O34*P34*Q34,"")</f>
         <v/>
       </c>
+      <c r="T34" s="53">
+        <f>IF(J34="","",100)</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1" s="25">
       <c r="A35" s="40" t="n"/>
@@ -2130,6 +2276,16 @@
       <c r="Q35" s="40" t="n"/>
       <c r="R35" s="41">
         <f>IF(COUNT(O35,P35,Q35)=3,O35*P35*Q35,"")</f>
+        <v/>
+      </c>
+      <c r="T35" s="53">
+        <f>IF(J35="","",100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="T36" s="53">
+        <f>IF(J36="","",100)</f>
         <v/>
       </c>
     </row>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -147,6 +147,11 @@
     <font>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="11">
@@ -287,7 +292,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -440,6 +445,10 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="18" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,7 +558,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Risk priority number — did the action actually reduce it?</a:t>
+              <a:t>Risk priority number — ranked, and did the action reduce it?</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -576,12 +585,12 @@
           <invertIfNegative val="0"/>
           <cat>
             <numRef>
-              <f>'FMEA'!$B$11:$B$36</f>
+              <f>'FMEA'!$V$11:$V$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FMEA'!$J$11:$J$36</f>
+              <f>'FMEA'!$W$11:$W$36</f>
             </numRef>
           </val>
         </ser>
@@ -602,12 +611,12 @@
           <invertIfNegative val="0"/>
           <cat>
             <numRef>
-              <f>'FMEA'!$B$11:$B$36</f>
+              <f>'FMEA'!$V$11:$V$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FMEA'!$R$11:$R$36</f>
+              <f>'FMEA'!$X$11:$X$36</f>
             </numRef>
           </val>
         </ser>
@@ -642,7 +651,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'FMEA'!$T$11:$T$36</f>
+              <f>'FMEA'!$Y$11:$Y$36</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -692,7 +701,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>26</col>
       <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
@@ -1040,7 +1049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T46"/>
+  <dimension ref="A1:Y46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="24" min="1" max="1"/>
@@ -1215,7 +1224,32 @@
           <t>New RPN</t>
         </is>
       </c>
-      <c r="T10" s="52" t="inlineStr">
+      <c r="T10" s="54" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="U10" s="52" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="V10" s="52" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="W10" s="52" t="inlineStr">
+        <is>
+          <t>RPN now</t>
+        </is>
+      </c>
+      <c r="X10" s="52" t="inlineStr">
+        <is>
+          <t>RPN after</t>
+        </is>
+      </c>
+      <c r="Y10" s="52" t="inlineStr">
         <is>
           <t>Act above</t>
         </is>
@@ -1298,8 +1332,27 @@
         <f>IF(COUNT(O11,P11,Q11)=3,O11*P11*Q11,"")</f>
         <v/>
       </c>
-      <c r="T11" s="53">
-        <f>IF(J11="","",100)</f>
+      <c r="T11" s="55">
+        <f>IF(J11="","",RANK(J11,$J$11:$J$36,0)+COUNTIF($J$11:J11,J11)-1)</f>
+        <v/>
+      </c>
+      <c r="U11" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U11,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W11" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U11,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X11" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U11,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y11" s="53">
+        <f>IF(W11="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1380,8 +1433,27 @@
         <f>IF(COUNT(O12,P12,Q12)=3,O12*P12*Q12,"")</f>
         <v/>
       </c>
-      <c r="T12" s="53">
-        <f>IF(J12="","",100)</f>
+      <c r="T12" s="55">
+        <f>IF(J12="","",RANK(J12,$J$11:$J$36,0)+COUNTIF($J$11:J12,J12)-1)</f>
+        <v/>
+      </c>
+      <c r="U12" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U12,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W12" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U12,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X12" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U12,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y12" s="53">
+        <f>IF(W12="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1462,8 +1534,27 @@
         <f>IF(COUNT(O13,P13,Q13)=3,O13*P13*Q13,"")</f>
         <v/>
       </c>
-      <c r="T13" s="53">
-        <f>IF(J13="","",100)</f>
+      <c r="T13" s="55">
+        <f>IF(J13="","",RANK(J13,$J$11:$J$36,0)+COUNTIF($J$11:J13,J13)-1)</f>
+        <v/>
+      </c>
+      <c r="U13" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U13,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W13" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U13,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X13" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U13,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y13" s="53">
+        <f>IF(W13="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1544,8 +1635,27 @@
         <f>IF(COUNT(O14,P14,Q14)=3,O14*P14*Q14,"")</f>
         <v/>
       </c>
-      <c r="T14" s="53">
-        <f>IF(J14="","",100)</f>
+      <c r="T14" s="55">
+        <f>IF(J14="","",RANK(J14,$J$11:$J$36,0)+COUNTIF($J$11:J14,J14)-1)</f>
+        <v/>
+      </c>
+      <c r="U14" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="V14" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U14,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W14" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U14,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X14" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U14,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y14" s="53">
+        <f>IF(W14="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1626,8 +1736,27 @@
         <f>IF(COUNT(O15,P15,Q15)=3,O15*P15*Q15,"")</f>
         <v/>
       </c>
-      <c r="T15" s="53">
-        <f>IF(J15="","",100)</f>
+      <c r="T15" s="55">
+        <f>IF(J15="","",RANK(J15,$J$11:$J$36,0)+COUNTIF($J$11:J15,J15)-1)</f>
+        <v/>
+      </c>
+      <c r="U15" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="V15" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U15,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W15" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U15,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X15" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U15,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y15" s="53">
+        <f>IF(W15="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1708,8 +1837,27 @@
         <f>IF(COUNT(O16,P16,Q16)=3,O16*P16*Q16,"")</f>
         <v/>
       </c>
-      <c r="T16" s="53">
-        <f>IF(J16="","",100)</f>
+      <c r="T16" s="55">
+        <f>IF(J16="","",RANK(J16,$J$11:$J$36,0)+COUNTIF($J$11:J16,J16)-1)</f>
+        <v/>
+      </c>
+      <c r="U16" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U16,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W16" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U16,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X16" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U16,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y16" s="53">
+        <f>IF(W16="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1738,8 +1886,27 @@
         <f>IF(COUNT(O17,P17,Q17)=3,O17*P17*Q17,"")</f>
         <v/>
       </c>
-      <c r="T17" s="53">
-        <f>IF(J17="","",100)</f>
+      <c r="T17" s="55">
+        <f>IF(J17="","",RANK(J17,$J$11:$J$36,0)+COUNTIF($J$11:J17,J17)-1)</f>
+        <v/>
+      </c>
+      <c r="U17" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="V17" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U17,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W17" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U17,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X17" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U17,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y17" s="53">
+        <f>IF(W17="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1768,8 +1935,27 @@
         <f>IF(COUNT(O18,P18,Q18)=3,O18*P18*Q18,"")</f>
         <v/>
       </c>
-      <c r="T18" s="53">
-        <f>IF(J18="","",100)</f>
+      <c r="T18" s="55">
+        <f>IF(J18="","",RANK(J18,$J$11:$J$36,0)+COUNTIF($J$11:J18,J18)-1)</f>
+        <v/>
+      </c>
+      <c r="U18" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="V18" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U18,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W18" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U18,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X18" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U18,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y18" s="53">
+        <f>IF(W18="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1798,8 +1984,27 @@
         <f>IF(COUNT(O19,P19,Q19)=3,O19*P19*Q19,"")</f>
         <v/>
       </c>
-      <c r="T19" s="53">
-        <f>IF(J19="","",100)</f>
+      <c r="T19" s="55">
+        <f>IF(J19="","",RANK(J19,$J$11:$J$36,0)+COUNTIF($J$11:J19,J19)-1)</f>
+        <v/>
+      </c>
+      <c r="U19" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="V19" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U19,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W19" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U19,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X19" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U19,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y19" s="53">
+        <f>IF(W19="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1828,8 +2033,27 @@
         <f>IF(COUNT(O20,P20,Q20)=3,O20*P20*Q20,"")</f>
         <v/>
       </c>
-      <c r="T20" s="53">
-        <f>IF(J20="","",100)</f>
+      <c r="T20" s="55">
+        <f>IF(J20="","",RANK(J20,$J$11:$J$36,0)+COUNTIF($J$11:J20,J20)-1)</f>
+        <v/>
+      </c>
+      <c r="U20" s="56" t="n">
+        <v>10</v>
+      </c>
+      <c r="V20" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U20,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W20" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U20,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X20" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U20,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y20" s="53">
+        <f>IF(W20="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1858,8 +2082,27 @@
         <f>IF(COUNT(O21,P21,Q21)=3,O21*P21*Q21,"")</f>
         <v/>
       </c>
-      <c r="T21" s="53">
-        <f>IF(J21="","",100)</f>
+      <c r="T21" s="55">
+        <f>IF(J21="","",RANK(J21,$J$11:$J$36,0)+COUNTIF($J$11:J21,J21)-1)</f>
+        <v/>
+      </c>
+      <c r="U21" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="V21" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U21,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W21" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U21,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X21" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U21,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y21" s="53">
+        <f>IF(W21="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1888,8 +2131,27 @@
         <f>IF(COUNT(O22,P22,Q22)=3,O22*P22*Q22,"")</f>
         <v/>
       </c>
-      <c r="T22" s="53">
-        <f>IF(J22="","",100)</f>
+      <c r="T22" s="55">
+        <f>IF(J22="","",RANK(J22,$J$11:$J$36,0)+COUNTIF($J$11:J22,J22)-1)</f>
+        <v/>
+      </c>
+      <c r="U22" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="V22" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U22,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W22" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U22,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X22" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U22,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y22" s="53">
+        <f>IF(W22="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1918,8 +2180,27 @@
         <f>IF(COUNT(O23,P23,Q23)=3,O23*P23*Q23,"")</f>
         <v/>
       </c>
-      <c r="T23" s="53">
-        <f>IF(J23="","",100)</f>
+      <c r="T23" s="55">
+        <f>IF(J23="","",RANK(J23,$J$11:$J$36,0)+COUNTIF($J$11:J23,J23)-1)</f>
+        <v/>
+      </c>
+      <c r="U23" s="56" t="n">
+        <v>13</v>
+      </c>
+      <c r="V23" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U23,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W23" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U23,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X23" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U23,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y23" s="53">
+        <f>IF(W23="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1948,8 +2229,27 @@
         <f>IF(COUNT(O24,P24,Q24)=3,O24*P24*Q24,"")</f>
         <v/>
       </c>
-      <c r="T24" s="53">
-        <f>IF(J24="","",100)</f>
+      <c r="T24" s="55">
+        <f>IF(J24="","",RANK(J24,$J$11:$J$36,0)+COUNTIF($J$11:J24,J24)-1)</f>
+        <v/>
+      </c>
+      <c r="U24" s="56" t="n">
+        <v>14</v>
+      </c>
+      <c r="V24" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U24,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W24" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U24,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X24" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U24,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y24" s="53">
+        <f>IF(W24="","",100)</f>
         <v/>
       </c>
     </row>
@@ -1978,8 +2278,27 @@
         <f>IF(COUNT(O25,P25,Q25)=3,O25*P25*Q25,"")</f>
         <v/>
       </c>
-      <c r="T25" s="53">
-        <f>IF(J25="","",100)</f>
+      <c r="T25" s="55">
+        <f>IF(J25="","",RANK(J25,$J$11:$J$36,0)+COUNTIF($J$11:J25,J25)-1)</f>
+        <v/>
+      </c>
+      <c r="U25" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="V25" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U25,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W25" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U25,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X25" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U25,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y25" s="53">
+        <f>IF(W25="","",100)</f>
         <v/>
       </c>
     </row>
@@ -2008,8 +2327,27 @@
         <f>IF(COUNT(O26,P26,Q26)=3,O26*P26*Q26,"")</f>
         <v/>
       </c>
-      <c r="T26" s="53">
-        <f>IF(J26="","",100)</f>
+      <c r="T26" s="55">
+        <f>IF(J26="","",RANK(J26,$J$11:$J$36,0)+COUNTIF($J$11:J26,J26)-1)</f>
+        <v/>
+      </c>
+      <c r="U26" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="V26" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U26,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W26" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U26,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X26" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U26,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y26" s="53">
+        <f>IF(W26="","",100)</f>
         <v/>
       </c>
     </row>
@@ -2038,8 +2376,27 @@
         <f>IF(COUNT(O27,P27,Q27)=3,O27*P27*Q27,"")</f>
         <v/>
       </c>
-      <c r="T27" s="53">
-        <f>IF(J27="","",100)</f>
+      <c r="T27" s="55">
+        <f>IF(J27="","",RANK(J27,$J$11:$J$36,0)+COUNTIF($J$11:J27,J27)-1)</f>
+        <v/>
+      </c>
+      <c r="U27" s="56" t="n">
+        <v>17</v>
+      </c>
+      <c r="V27" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U27,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W27" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U27,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X27" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U27,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y27" s="53">
+        <f>IF(W27="","",100)</f>
         <v/>
       </c>
     </row>
@@ -2068,8 +2425,27 @@
         <f>IF(COUNT(O28,P28,Q28)=3,O28*P28*Q28,"")</f>
         <v/>
       </c>
-      <c r="T28" s="53">
-        <f>IF(J28="","",100)</f>
+      <c r="T28" s="55">
+        <f>IF(J28="","",RANK(J28,$J$11:$J$36,0)+COUNTIF($J$11:J28,J28)-1)</f>
+        <v/>
+      </c>
+      <c r="U28" s="56" t="n">
+        <v>18</v>
+      </c>
+      <c r="V28" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U28,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W28" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U28,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X28" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U28,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y28" s="53">
+        <f>IF(W28="","",100)</f>
         <v/>
       </c>
     </row>
@@ -2098,8 +2474,27 @@
         <f>IF(COUNT(O29,P29,Q29)=3,O29*P29*Q29,"")</f>
         <v/>
       </c>
-      <c r="T29" s="53">
-        <f>IF(J29="","",100)</f>
+      <c r="T29" s="55">
+        <f>IF(J29="","",RANK(J29,$J$11:$J$36,0)+COUNTIF($J$11:J29,J29)-1)</f>
+        <v/>
+      </c>
+      <c r="U29" s="56" t="n">
+        <v>19</v>
+      </c>
+      <c r="V29" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U29,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W29" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U29,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X29" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U29,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y29" s="53">
+        <f>IF(W29="","",100)</f>
         <v/>
       </c>
     </row>
@@ -2128,8 +2523,27 @@
         <f>IF(COUNT(O30,P30,Q30)=3,O30*P30*Q30,"")</f>
         <v/>
       </c>
-      <c r="T30" s="53">
-        <f>IF(J30="","",100)</f>
+      <c r="T30" s="55">
+        <f>IF(J30="","",RANK(J30,$J$11:$J$36,0)+COUNTIF($J$11:J30,J30)-1)</f>
+        <v/>
+      </c>
+      <c r="U30" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="V30" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U30,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W30" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U30,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X30" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U30,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y30" s="53">
+        <f>IF(W30="","",100)</f>
         <v/>
       </c>
     </row>
@@ -2158,8 +2572,27 @@
         <f>IF(COUNT(O31,P31,Q31)=3,O31*P31*Q31,"")</f>
         <v/>
       </c>
-      <c r="T31" s="53">
-        <f>IF(J31="","",100)</f>
+      <c r="T31" s="55">
+        <f>IF(J31="","",RANK(J31,$J$11:$J$36,0)+COUNTIF($J$11:J31,J31)-1)</f>
+        <v/>
+      </c>
+      <c r="U31" s="56" t="n">
+        <v>21</v>
+      </c>
+      <c r="V31" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U31,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W31" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U31,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X31" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U31,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y31" s="53">
+        <f>IF(W31="","",100)</f>
         <v/>
       </c>
     </row>
@@ -2188,8 +2621,27 @@
         <f>IF(COUNT(O32,P32,Q32)=3,O32*P32*Q32,"")</f>
         <v/>
       </c>
-      <c r="T32" s="53">
-        <f>IF(J32="","",100)</f>
+      <c r="T32" s="55">
+        <f>IF(J32="","",RANK(J32,$J$11:$J$36,0)+COUNTIF($J$11:J32,J32)-1)</f>
+        <v/>
+      </c>
+      <c r="U32" s="56" t="n">
+        <v>22</v>
+      </c>
+      <c r="V32" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U32,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W32" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U32,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X32" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U32,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y32" s="53">
+        <f>IF(W32="","",100)</f>
         <v/>
       </c>
     </row>
@@ -2218,8 +2670,27 @@
         <f>IF(COUNT(O33,P33,Q33)=3,O33*P33*Q33,"")</f>
         <v/>
       </c>
-      <c r="T33" s="53">
-        <f>IF(J33="","",100)</f>
+      <c r="T33" s="55">
+        <f>IF(J33="","",RANK(J33,$J$11:$J$36,0)+COUNTIF($J$11:J33,J33)-1)</f>
+        <v/>
+      </c>
+      <c r="U33" s="56" t="n">
+        <v>23</v>
+      </c>
+      <c r="V33" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U33,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W33" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U33,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X33" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U33,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y33" s="53">
+        <f>IF(W33="","",100)</f>
         <v/>
       </c>
     </row>
@@ -2248,8 +2719,27 @@
         <f>IF(COUNT(O34,P34,Q34)=3,O34*P34*Q34,"")</f>
         <v/>
       </c>
-      <c r="T34" s="53">
-        <f>IF(J34="","",100)</f>
+      <c r="T34" s="55">
+        <f>IF(J34="","",RANK(J34,$J$11:$J$36,0)+COUNTIF($J$11:J34,J34)-1)</f>
+        <v/>
+      </c>
+      <c r="U34" s="56" t="n">
+        <v>24</v>
+      </c>
+      <c r="V34" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U34,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W34" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U34,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X34" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U34,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y34" s="53">
+        <f>IF(W34="","",100)</f>
         <v/>
       </c>
     </row>
@@ -2278,14 +2768,52 @@
         <f>IF(COUNT(O35,P35,Q35)=3,O35*P35*Q35,"")</f>
         <v/>
       </c>
-      <c r="T35" s="53">
-        <f>IF(J35="","",100)</f>
+      <c r="T35" s="55">
+        <f>IF(J35="","",RANK(J35,$J$11:$J$36,0)+COUNTIF($J$11:J35,J35)-1)</f>
+        <v/>
+      </c>
+      <c r="U35" s="56" t="n">
+        <v>25</v>
+      </c>
+      <c r="V35" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U35,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W35" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U35,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X35" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U35,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y35" s="53">
+        <f>IF(W35="","",100)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="T36" s="53">
-        <f>IF(J36="","",100)</f>
+      <c r="T36" s="55">
+        <f>IF(J36="","",RANK(J36,$J$11:$J$36,0)+COUNTIF($J$11:J36,J36)-1)</f>
+        <v/>
+      </c>
+      <c r="U36" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="V36" s="57">
+        <f>IFERROR(INDEX($B$11:$B$36,MATCH(U36,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="W36" s="53">
+        <f>IFERROR(INDEX($J$11:$J$36,MATCH(U36,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="X36" s="53">
+        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U36,$T$11:$T$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="Y36" s="53">
+        <f>IF(W36="","",100)</f>
         <v/>
       </c>
     </row>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -154,7 +154,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -211,6 +211,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -292,7 +297,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -449,6 +454,7 @@
     <xf numFmtId="1" fontId="18" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -631,7 +637,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Act above this (RPN 100)</v>
+            <v>Act above this threshold</v>
           </tx>
           <spPr>
             <a:ln w="18000">
@@ -1352,7 +1358,7 @@
         <v/>
       </c>
       <c r="Y11" s="53">
-        <f>IF(W11="","",100)</f>
+        <f>IF(W11="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -1453,7 +1459,7 @@
         <v/>
       </c>
       <c r="Y12" s="53">
-        <f>IF(W12="","",100)</f>
+        <f>IF(W12="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -1554,7 +1560,7 @@
         <v/>
       </c>
       <c r="Y13" s="53">
-        <f>IF(W13="","",100)</f>
+        <f>IF(W13="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -1655,7 +1661,7 @@
         <v/>
       </c>
       <c r="Y14" s="53">
-        <f>IF(W14="","",100)</f>
+        <f>IF(W14="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -1756,7 +1762,7 @@
         <v/>
       </c>
       <c r="Y15" s="53">
-        <f>IF(W15="","",100)</f>
+        <f>IF(W15="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -1857,7 +1863,7 @@
         <v/>
       </c>
       <c r="Y16" s="53">
-        <f>IF(W16="","",100)</f>
+        <f>IF(W16="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -1906,7 +1912,7 @@
         <v/>
       </c>
       <c r="Y17" s="53">
-        <f>IF(W17="","",100)</f>
+        <f>IF(W17="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1961,7 @@
         <v/>
       </c>
       <c r="Y18" s="53">
-        <f>IF(W18="","",100)</f>
+        <f>IF(W18="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2004,7 +2010,7 @@
         <v/>
       </c>
       <c r="Y19" s="53">
-        <f>IF(W19="","",100)</f>
+        <f>IF(W19="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2053,7 +2059,7 @@
         <v/>
       </c>
       <c r="Y20" s="53">
-        <f>IF(W20="","",100)</f>
+        <f>IF(W20="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2102,7 +2108,7 @@
         <v/>
       </c>
       <c r="Y21" s="53">
-        <f>IF(W21="","",100)</f>
+        <f>IF(W21="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2151,7 +2157,7 @@
         <v/>
       </c>
       <c r="Y22" s="53">
-        <f>IF(W22="","",100)</f>
+        <f>IF(W22="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2200,7 +2206,7 @@
         <v/>
       </c>
       <c r="Y23" s="53">
-        <f>IF(W23="","",100)</f>
+        <f>IF(W23="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2249,7 +2255,7 @@
         <v/>
       </c>
       <c r="Y24" s="53">
-        <f>IF(W24="","",100)</f>
+        <f>IF(W24="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2298,7 +2304,7 @@
         <v/>
       </c>
       <c r="Y25" s="53">
-        <f>IF(W25="","",100)</f>
+        <f>IF(W25="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2347,7 +2353,7 @@
         <v/>
       </c>
       <c r="Y26" s="53">
-        <f>IF(W26="","",100)</f>
+        <f>IF(W26="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2396,7 +2402,7 @@
         <v/>
       </c>
       <c r="Y27" s="53">
-        <f>IF(W27="","",100)</f>
+        <f>IF(W27="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2445,7 +2451,7 @@
         <v/>
       </c>
       <c r="Y28" s="53">
-        <f>IF(W28="","",100)</f>
+        <f>IF(W28="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2494,7 +2500,7 @@
         <v/>
       </c>
       <c r="Y29" s="53">
-        <f>IF(W29="","",100)</f>
+        <f>IF(W29="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2543,7 +2549,7 @@
         <v/>
       </c>
       <c r="Y30" s="53">
-        <f>IF(W30="","",100)</f>
+        <f>IF(W30="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2592,7 +2598,7 @@
         <v/>
       </c>
       <c r="Y31" s="53">
-        <f>IF(W31="","",100)</f>
+        <f>IF(W31="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2641,7 +2647,7 @@
         <v/>
       </c>
       <c r="Y32" s="53">
-        <f>IF(W32="","",100)</f>
+        <f>IF(W32="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2690,7 +2696,7 @@
         <v/>
       </c>
       <c r="Y33" s="53">
-        <f>IF(W33="","",100)</f>
+        <f>IF(W33="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2739,7 +2745,7 @@
         <v/>
       </c>
       <c r="Y34" s="53">
-        <f>IF(W34="","",100)</f>
+        <f>IF(W34="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2788,7 +2794,7 @@
         <v/>
       </c>
       <c r="Y35" s="53">
-        <f>IF(W35="","",100)</f>
+        <f>IF(W35="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2813,7 +2819,7 @@
         <v/>
       </c>
       <c r="Y36" s="53">
-        <f>IF(W36="","",100)</f>
+        <f>IF(W36="","",$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2849,11 +2855,11 @@
     <row r="40" ht="15" customHeight="1" s="25">
       <c r="A40" s="42" t="inlineStr">
         <is>
-          <t>Above 200 (act now)</t>
+          <t>Above the action threshold (act now)</t>
         </is>
       </c>
       <c r="D40" s="43">
-        <f>COUNTIF(J11:J35,"&gt;=200")</f>
+        <f>COUNTIF(J11:J35,"&gt;="&amp;$D$45)</f>
         <v/>
       </c>
     </row>
@@ -2899,6 +2905,21 @@
       <c r="D44" s="44">
         <f>IFERROR(1-AVERAGE(R11:R35)/AVERAGEIF(R11:R35,"&gt;0",J11:J35),"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="52" t="inlineStr">
+        <is>
+          <t>Act above this RPN</t>
+        </is>
+      </c>
+      <c r="D45" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E45" s="54" t="inlineStr">
+        <is>
+          <t>The conventional line is 100-200. Whatever you set here drives the chart line and the count above.</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="39" customHeight="1" s="25">

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -604,7 +604,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <v>RPN after</v>
+            <v>RPN after (no re-score = no reduction)</v>
           </tx>
           <spPr>
             <a:solidFill>
@@ -1230,6 +1230,11 @@
           <t>New RPN</t>
         </is>
       </c>
+      <c r="S10" s="52" t="inlineStr">
+        <is>
+          <t>RPN after (no re-score = no reduction)</t>
+        </is>
+      </c>
       <c r="T10" s="54" t="inlineStr">
         <is>
           <t>rank</t>
@@ -1338,6 +1343,10 @@
         <f>IF(COUNT(O11,P11,Q11)=3,O11*P11*Q11,"")</f>
         <v/>
       </c>
+      <c r="S11" s="53">
+        <f>IF($J11="","",IF(COUNT($O11,$P11,$Q11)=3,$R11,$J11))</f>
+        <v/>
+      </c>
       <c r="T11" s="55">
         <f>IF(J11="","",RANK(J11,$J$11:$J$36,0)+COUNTIF($J$11:J11,J11)-1)</f>
         <v/>
@@ -1354,7 +1363,7 @@
         <v/>
       </c>
       <c r="X11" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U11,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U11,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y11" s="53">
@@ -1439,6 +1448,10 @@
         <f>IF(COUNT(O12,P12,Q12)=3,O12*P12*Q12,"")</f>
         <v/>
       </c>
+      <c r="S12" s="53">
+        <f>IF($J12="","",IF(COUNT($O12,$P12,$Q12)=3,$R12,$J12))</f>
+        <v/>
+      </c>
       <c r="T12" s="55">
         <f>IF(J12="","",RANK(J12,$J$11:$J$36,0)+COUNTIF($J$11:J12,J12)-1)</f>
         <v/>
@@ -1455,7 +1468,7 @@
         <v/>
       </c>
       <c r="X12" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U12,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U12,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y12" s="53">
@@ -1540,6 +1553,10 @@
         <f>IF(COUNT(O13,P13,Q13)=3,O13*P13*Q13,"")</f>
         <v/>
       </c>
+      <c r="S13" s="53">
+        <f>IF($J13="","",IF(COUNT($O13,$P13,$Q13)=3,$R13,$J13))</f>
+        <v/>
+      </c>
       <c r="T13" s="55">
         <f>IF(J13="","",RANK(J13,$J$11:$J$36,0)+COUNTIF($J$11:J13,J13)-1)</f>
         <v/>
@@ -1556,7 +1573,7 @@
         <v/>
       </c>
       <c r="X13" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U13,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U13,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y13" s="53">
@@ -1641,6 +1658,10 @@
         <f>IF(COUNT(O14,P14,Q14)=3,O14*P14*Q14,"")</f>
         <v/>
       </c>
+      <c r="S14" s="53">
+        <f>IF($J14="","",IF(COUNT($O14,$P14,$Q14)=3,$R14,$J14))</f>
+        <v/>
+      </c>
       <c r="T14" s="55">
         <f>IF(J14="","",RANK(J14,$J$11:$J$36,0)+COUNTIF($J$11:J14,J14)-1)</f>
         <v/>
@@ -1657,7 +1678,7 @@
         <v/>
       </c>
       <c r="X14" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U14,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U14,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y14" s="53">
@@ -1742,6 +1763,10 @@
         <f>IF(COUNT(O15,P15,Q15)=3,O15*P15*Q15,"")</f>
         <v/>
       </c>
+      <c r="S15" s="53">
+        <f>IF($J15="","",IF(COUNT($O15,$P15,$Q15)=3,$R15,$J15))</f>
+        <v/>
+      </c>
       <c r="T15" s="55">
         <f>IF(J15="","",RANK(J15,$J$11:$J$36,0)+COUNTIF($J$11:J15,J15)-1)</f>
         <v/>
@@ -1758,7 +1783,7 @@
         <v/>
       </c>
       <c r="X15" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U15,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U15,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y15" s="53">
@@ -1843,6 +1868,10 @@
         <f>IF(COUNT(O16,P16,Q16)=3,O16*P16*Q16,"")</f>
         <v/>
       </c>
+      <c r="S16" s="53">
+        <f>IF($J16="","",IF(COUNT($O16,$P16,$Q16)=3,$R16,$J16))</f>
+        <v/>
+      </c>
       <c r="T16" s="55">
         <f>IF(J16="","",RANK(J16,$J$11:$J$36,0)+COUNTIF($J$11:J16,J16)-1)</f>
         <v/>
@@ -1859,7 +1888,7 @@
         <v/>
       </c>
       <c r="X16" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U16,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U16,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y16" s="53">
@@ -1892,6 +1921,10 @@
         <f>IF(COUNT(O17,P17,Q17)=3,O17*P17*Q17,"")</f>
         <v/>
       </c>
+      <c r="S17" s="53">
+        <f>IF($J17="","",IF(COUNT($O17,$P17,$Q17)=3,$R17,$J17))</f>
+        <v/>
+      </c>
       <c r="T17" s="55">
         <f>IF(J17="","",RANK(J17,$J$11:$J$36,0)+COUNTIF($J$11:J17,J17)-1)</f>
         <v/>
@@ -1908,7 +1941,7 @@
         <v/>
       </c>
       <c r="X17" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U17,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U17,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y17" s="53">
@@ -1941,6 +1974,10 @@
         <f>IF(COUNT(O18,P18,Q18)=3,O18*P18*Q18,"")</f>
         <v/>
       </c>
+      <c r="S18" s="53">
+        <f>IF($J18="","",IF(COUNT($O18,$P18,$Q18)=3,$R18,$J18))</f>
+        <v/>
+      </c>
       <c r="T18" s="55">
         <f>IF(J18="","",RANK(J18,$J$11:$J$36,0)+COUNTIF($J$11:J18,J18)-1)</f>
         <v/>
@@ -1957,7 +1994,7 @@
         <v/>
       </c>
       <c r="X18" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U18,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U18,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y18" s="53">
@@ -1990,6 +2027,10 @@
         <f>IF(COUNT(O19,P19,Q19)=3,O19*P19*Q19,"")</f>
         <v/>
       </c>
+      <c r="S19" s="53">
+        <f>IF($J19="","",IF(COUNT($O19,$P19,$Q19)=3,$R19,$J19))</f>
+        <v/>
+      </c>
       <c r="T19" s="55">
         <f>IF(J19="","",RANK(J19,$J$11:$J$36,0)+COUNTIF($J$11:J19,J19)-1)</f>
         <v/>
@@ -2006,7 +2047,7 @@
         <v/>
       </c>
       <c r="X19" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U19,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U19,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y19" s="53">
@@ -2039,6 +2080,10 @@
         <f>IF(COUNT(O20,P20,Q20)=3,O20*P20*Q20,"")</f>
         <v/>
       </c>
+      <c r="S20" s="53">
+        <f>IF($J20="","",IF(COUNT($O20,$P20,$Q20)=3,$R20,$J20))</f>
+        <v/>
+      </c>
       <c r="T20" s="55">
         <f>IF(J20="","",RANK(J20,$J$11:$J$36,0)+COUNTIF($J$11:J20,J20)-1)</f>
         <v/>
@@ -2055,7 +2100,7 @@
         <v/>
       </c>
       <c r="X20" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U20,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U20,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y20" s="53">
@@ -2088,6 +2133,10 @@
         <f>IF(COUNT(O21,P21,Q21)=3,O21*P21*Q21,"")</f>
         <v/>
       </c>
+      <c r="S21" s="53">
+        <f>IF($J21="","",IF(COUNT($O21,$P21,$Q21)=3,$R21,$J21))</f>
+        <v/>
+      </c>
       <c r="T21" s="55">
         <f>IF(J21="","",RANK(J21,$J$11:$J$36,0)+COUNTIF($J$11:J21,J21)-1)</f>
         <v/>
@@ -2104,7 +2153,7 @@
         <v/>
       </c>
       <c r="X21" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U21,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U21,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y21" s="53">
@@ -2137,6 +2186,10 @@
         <f>IF(COUNT(O22,P22,Q22)=3,O22*P22*Q22,"")</f>
         <v/>
       </c>
+      <c r="S22" s="53">
+        <f>IF($J22="","",IF(COUNT($O22,$P22,$Q22)=3,$R22,$J22))</f>
+        <v/>
+      </c>
       <c r="T22" s="55">
         <f>IF(J22="","",RANK(J22,$J$11:$J$36,0)+COUNTIF($J$11:J22,J22)-1)</f>
         <v/>
@@ -2153,7 +2206,7 @@
         <v/>
       </c>
       <c r="X22" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U22,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U22,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y22" s="53">
@@ -2186,6 +2239,10 @@
         <f>IF(COUNT(O23,P23,Q23)=3,O23*P23*Q23,"")</f>
         <v/>
       </c>
+      <c r="S23" s="53">
+        <f>IF($J23="","",IF(COUNT($O23,$P23,$Q23)=3,$R23,$J23))</f>
+        <v/>
+      </c>
       <c r="T23" s="55">
         <f>IF(J23="","",RANK(J23,$J$11:$J$36,0)+COUNTIF($J$11:J23,J23)-1)</f>
         <v/>
@@ -2202,7 +2259,7 @@
         <v/>
       </c>
       <c r="X23" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U23,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U23,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y23" s="53">
@@ -2235,6 +2292,10 @@
         <f>IF(COUNT(O24,P24,Q24)=3,O24*P24*Q24,"")</f>
         <v/>
       </c>
+      <c r="S24" s="53">
+        <f>IF($J24="","",IF(COUNT($O24,$P24,$Q24)=3,$R24,$J24))</f>
+        <v/>
+      </c>
       <c r="T24" s="55">
         <f>IF(J24="","",RANK(J24,$J$11:$J$36,0)+COUNTIF($J$11:J24,J24)-1)</f>
         <v/>
@@ -2251,7 +2312,7 @@
         <v/>
       </c>
       <c r="X24" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U24,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U24,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y24" s="53">
@@ -2284,6 +2345,10 @@
         <f>IF(COUNT(O25,P25,Q25)=3,O25*P25*Q25,"")</f>
         <v/>
       </c>
+      <c r="S25" s="53">
+        <f>IF($J25="","",IF(COUNT($O25,$P25,$Q25)=3,$R25,$J25))</f>
+        <v/>
+      </c>
       <c r="T25" s="55">
         <f>IF(J25="","",RANK(J25,$J$11:$J$36,0)+COUNTIF($J$11:J25,J25)-1)</f>
         <v/>
@@ -2300,7 +2365,7 @@
         <v/>
       </c>
       <c r="X25" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U25,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U25,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y25" s="53">
@@ -2333,6 +2398,10 @@
         <f>IF(COUNT(O26,P26,Q26)=3,O26*P26*Q26,"")</f>
         <v/>
       </c>
+      <c r="S26" s="53">
+        <f>IF($J26="","",IF(COUNT($O26,$P26,$Q26)=3,$R26,$J26))</f>
+        <v/>
+      </c>
       <c r="T26" s="55">
         <f>IF(J26="","",RANK(J26,$J$11:$J$36,0)+COUNTIF($J$11:J26,J26)-1)</f>
         <v/>
@@ -2349,7 +2418,7 @@
         <v/>
       </c>
       <c r="X26" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U26,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U26,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y26" s="53">
@@ -2382,6 +2451,10 @@
         <f>IF(COUNT(O27,P27,Q27)=3,O27*P27*Q27,"")</f>
         <v/>
       </c>
+      <c r="S27" s="53">
+        <f>IF($J27="","",IF(COUNT($O27,$P27,$Q27)=3,$R27,$J27))</f>
+        <v/>
+      </c>
       <c r="T27" s="55">
         <f>IF(J27="","",RANK(J27,$J$11:$J$36,0)+COUNTIF($J$11:J27,J27)-1)</f>
         <v/>
@@ -2398,7 +2471,7 @@
         <v/>
       </c>
       <c r="X27" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U27,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U27,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y27" s="53">
@@ -2431,6 +2504,10 @@
         <f>IF(COUNT(O28,P28,Q28)=3,O28*P28*Q28,"")</f>
         <v/>
       </c>
+      <c r="S28" s="53">
+        <f>IF($J28="","",IF(COUNT($O28,$P28,$Q28)=3,$R28,$J28))</f>
+        <v/>
+      </c>
       <c r="T28" s="55">
         <f>IF(J28="","",RANK(J28,$J$11:$J$36,0)+COUNTIF($J$11:J28,J28)-1)</f>
         <v/>
@@ -2447,7 +2524,7 @@
         <v/>
       </c>
       <c r="X28" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U28,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U28,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y28" s="53">
@@ -2480,6 +2557,10 @@
         <f>IF(COUNT(O29,P29,Q29)=3,O29*P29*Q29,"")</f>
         <v/>
       </c>
+      <c r="S29" s="53">
+        <f>IF($J29="","",IF(COUNT($O29,$P29,$Q29)=3,$R29,$J29))</f>
+        <v/>
+      </c>
       <c r="T29" s="55">
         <f>IF(J29="","",RANK(J29,$J$11:$J$36,0)+COUNTIF($J$11:J29,J29)-1)</f>
         <v/>
@@ -2496,7 +2577,7 @@
         <v/>
       </c>
       <c r="X29" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U29,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U29,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y29" s="53">
@@ -2529,6 +2610,10 @@
         <f>IF(COUNT(O30,P30,Q30)=3,O30*P30*Q30,"")</f>
         <v/>
       </c>
+      <c r="S30" s="53">
+        <f>IF($J30="","",IF(COUNT($O30,$P30,$Q30)=3,$R30,$J30))</f>
+        <v/>
+      </c>
       <c r="T30" s="55">
         <f>IF(J30="","",RANK(J30,$J$11:$J$36,0)+COUNTIF($J$11:J30,J30)-1)</f>
         <v/>
@@ -2545,7 +2630,7 @@
         <v/>
       </c>
       <c r="X30" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U30,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U30,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y30" s="53">
@@ -2578,6 +2663,10 @@
         <f>IF(COUNT(O31,P31,Q31)=3,O31*P31*Q31,"")</f>
         <v/>
       </c>
+      <c r="S31" s="53">
+        <f>IF($J31="","",IF(COUNT($O31,$P31,$Q31)=3,$R31,$J31))</f>
+        <v/>
+      </c>
       <c r="T31" s="55">
         <f>IF(J31="","",RANK(J31,$J$11:$J$36,0)+COUNTIF($J$11:J31,J31)-1)</f>
         <v/>
@@ -2594,7 +2683,7 @@
         <v/>
       </c>
       <c r="X31" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U31,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U31,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y31" s="53">
@@ -2627,6 +2716,10 @@
         <f>IF(COUNT(O32,P32,Q32)=3,O32*P32*Q32,"")</f>
         <v/>
       </c>
+      <c r="S32" s="53">
+        <f>IF($J32="","",IF(COUNT($O32,$P32,$Q32)=3,$R32,$J32))</f>
+        <v/>
+      </c>
       <c r="T32" s="55">
         <f>IF(J32="","",RANK(J32,$J$11:$J$36,0)+COUNTIF($J$11:J32,J32)-1)</f>
         <v/>
@@ -2643,7 +2736,7 @@
         <v/>
       </c>
       <c r="X32" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U32,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U32,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y32" s="53">
@@ -2676,6 +2769,10 @@
         <f>IF(COUNT(O33,P33,Q33)=3,O33*P33*Q33,"")</f>
         <v/>
       </c>
+      <c r="S33" s="53">
+        <f>IF($J33="","",IF(COUNT($O33,$P33,$Q33)=3,$R33,$J33))</f>
+        <v/>
+      </c>
       <c r="T33" s="55">
         <f>IF(J33="","",RANK(J33,$J$11:$J$36,0)+COUNTIF($J$11:J33,J33)-1)</f>
         <v/>
@@ -2692,7 +2789,7 @@
         <v/>
       </c>
       <c r="X33" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U33,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U33,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y33" s="53">
@@ -2725,6 +2822,10 @@
         <f>IF(COUNT(O34,P34,Q34)=3,O34*P34*Q34,"")</f>
         <v/>
       </c>
+      <c r="S34" s="53">
+        <f>IF($J34="","",IF(COUNT($O34,$P34,$Q34)=3,$R34,$J34))</f>
+        <v/>
+      </c>
       <c r="T34" s="55">
         <f>IF(J34="","",RANK(J34,$J$11:$J$36,0)+COUNTIF($J$11:J34,J34)-1)</f>
         <v/>
@@ -2741,7 +2842,7 @@
         <v/>
       </c>
       <c r="X34" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U34,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U34,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y34" s="53">
@@ -2774,6 +2875,10 @@
         <f>IF(COUNT(O35,P35,Q35)=3,O35*P35*Q35,"")</f>
         <v/>
       </c>
+      <c r="S35" s="53">
+        <f>IF($J35="","",IF(COUNT($O35,$P35,$Q35)=3,$R35,$J35))</f>
+        <v/>
+      </c>
       <c r="T35" s="55">
         <f>IF(J35="","",RANK(J35,$J$11:$J$36,0)+COUNTIF($J$11:J35,J35)-1)</f>
         <v/>
@@ -2790,7 +2895,7 @@
         <v/>
       </c>
       <c r="X35" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U35,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U35,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y35" s="53">
@@ -2799,6 +2904,10 @@
       </c>
     </row>
     <row r="36">
+      <c r="S36" s="53">
+        <f>IF($J36="","",IF(COUNT($O36,$P36,$Q36)=3,$R36,$J36))</f>
+        <v/>
+      </c>
       <c r="T36" s="55">
         <f>IF(J36="","",RANK(J36,$J$11:$J$36,0)+COUNTIF($J$11:J36,J36)-1)</f>
         <v/>
@@ -2815,7 +2924,7 @@
         <v/>
       </c>
       <c r="X36" s="53">
-        <f>IFERROR(INDEX($R$11:$R$36,MATCH(U36,$T$11:$T$36,0)),"")</f>
+        <f>IFERROR(INDEX($S$11:$S$36,MATCH(U36,$T$11:$T$36,0)),"")</f>
         <v/>
       </c>
       <c r="Y36" s="53">

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -709,7 +709,7 @@
     <from>
       <col>26</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3600000"/>
@@ -1089,6 +1089,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="25">
       <c r="A4" s="33" t="inlineStr">
         <is>
@@ -1132,6 +1133,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="19.5" customHeight="1" s="25">
       <c r="A9" s="33" t="inlineStr">
         <is>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -677,8 +677,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -297,7 +297,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -455,6 +455,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1134,10 +1137,10 @@
       </c>
     </row>
     <row r="8"/>
-    <row r="9" ht="19.5" customHeight="1" s="25">
-      <c r="A9" s="33" t="inlineStr">
-        <is>
-          <t>SCORE EACH FAILURE MODE 1–10 ON SEVERITY, OCCURRENCE AND DETECTION. THE SCORING GUIDE IS ON THE NEXT SHEET.</t>
+    <row r="9" ht="24" customHeight="1" s="25">
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>SCORE EACH FAILURE MODE 1–10 ON SEVERITY, OCCURRENCE AND DETECTION. THE SCORING GUIDE IS ON THE NEXT SHEET.  ·  Key: RPN = risk priority number, severity x occurrence x detection</t>
         </is>
       </c>
     </row>
@@ -3114,6 +3117,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="25">
       <c r="A4" s="33" t="inlineStr">
         <is>
@@ -3217,6 +3221,7 @@
       <c r="E10" s="48" t="n"/>
       <c r="F10" s="49" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="19.5" customHeight="1" s="25">
       <c r="A12" s="33" t="inlineStr">
         <is>
@@ -3320,6 +3325,7 @@
       <c r="E18" s="48" t="n"/>
       <c r="F18" s="49" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="19.5" customHeight="1" s="25">
       <c r="A20" s="33" t="inlineStr">
         <is>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -297,7 +297,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -457,6 +457,15 @@
     <xf numFmtId="3" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -947,7 +956,7 @@
     <row r="6" ht="15" customHeight="1" s="25">
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>1.  Open the FMEA tab. Row 1 is a worked example — read it, then overwrite or delete it.</t>
+          <t>1.  Open the FMEA tab. The green rows are a worked example — read them, then overwrite them with your own failure modes.</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1136,12 @@
     <row r="7" ht="15" customHeight="1" s="25">
       <c r="A7" s="37" t="inlineStr">
         <is>
-          <t>Row 1 example</t>
+          <t>Green cells</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>A realistic worked example, so you can see the expected format. Delete or overwrite it.</t>
+          <t>A realistic worked example, so you can see the expected format and the sheet is not blank when you open it. Replace it with your own.</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1320,7 @@
       <c r="I11" s="50" t="n">
         <v>9</v>
       </c>
-      <c r="J11" s="39">
+      <c r="J11" s="60">
         <f>IF(COUNT(D11,F11,I11)=3,D11*F11*I11,"")</f>
         <v/>
       </c>
@@ -1344,7 +1353,7 @@
       <c r="Q11" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="R11" s="39">
+      <c r="R11" s="60">
         <f>IF(COUNT(O11,P11,Q11)=3,O11*P11*Q11,"")</f>
         <v/>
       </c>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -297,7 +297,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -466,6 +466,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1077,6 +1080,7 @@
     <col width="26" customWidth="1" style="24" min="5" max="5"/>
     <col width="6" customWidth="1" style="24" min="6" max="6"/>
     <col width="24" customWidth="1" style="24" min="7" max="8"/>
+    <col width="13" customWidth="1" style="25" min="8" max="8"/>
     <col width="6" customWidth="1" style="24" min="9" max="9"/>
     <col width="8" customWidth="1" style="24" min="10" max="10"/>
     <col width="30" customWidth="1" style="24" min="11" max="11"/>
@@ -1084,7 +1088,16 @@
     <col width="11" customWidth="1" style="24" min="13" max="13"/>
     <col width="26" customWidth="1" style="24" min="14" max="14"/>
     <col width="8" customWidth="1" style="24" min="15" max="17"/>
+    <col width="13" customWidth="1" style="25" min="16" max="16"/>
+    <col width="13" customWidth="1" style="25" min="17" max="17"/>
     <col width="9" customWidth="1" style="24" min="18" max="18"/>
+    <col width="13" customWidth="1" style="25" min="19" max="19"/>
+    <col width="13" customWidth="1" style="25" min="20" max="20"/>
+    <col width="13" customWidth="1" style="25" min="21" max="21"/>
+    <col width="13" customWidth="1" style="25" min="22" max="22"/>
+    <col width="13" customWidth="1" style="25" min="23" max="23"/>
+    <col width="13" customWidth="1" style="25" min="24" max="24"/>
+    <col width="13" customWidth="1" style="25" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="25">
@@ -1146,10 +1159,10 @@
       </c>
     </row>
     <row r="8"/>
-    <row r="9" ht="24" customHeight="1" s="25">
+    <row r="9" ht="276" customHeight="1" s="25">
       <c r="A9" s="59" t="inlineStr">
         <is>
-          <t>SCORE EACH FAILURE MODE 1–10 ON SEVERITY, OCCURRENCE AND DETECTION. THE SCORING GUIDE IS ON THE NEXT SHEET.  ·  Key: RPN = risk priority number, severity x occurrence x detection</t>
+          <t>SCORE EACH FAILURE MODE 1–10 ON SEVERITY, OCCURRENCE AND DETECTION. THE SCORING GUIDE IS ON THE NEXT SHEET.  ·  Key: Effect on the customer = what the person on the other end experiences, in their words, which is what SEV is scored against. 'Customer discovers it themselves and contacts us again' scores 7; 'margin leakage, caught in reconciliation' scores 4, because the customer never feels it (C11, C15) · SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says · OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see · Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should · DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve · RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks · New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%</t>
         </is>
       </c>
     </row>
@@ -1446,17 +1459,17 @@
       </c>
       <c r="N12" s="51" t="inlineStr">
         <is>
-          <t>Code list redesigned, pending release</t>
+          <t>Code list redesigned, pending release — not re-scored until live</t>
         </is>
       </c>
       <c r="O12" s="51" t="n">
         <v>6</v>
       </c>
       <c r="P12" s="51" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q12" s="51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R12" s="41">
         <f>IF(COUNT(O12,P12,Q12)=3,O12*P12*Q12,"")</f>
@@ -3019,16 +3032,21 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="25">
+    <row r="44" ht="26" customHeight="1" s="25">
       <c r="A44" s="42" t="inlineStr">
         <is>
-          <t>Risk reduction (on remediated rows)</t>
+          <t>Risk reduction (on remediated rows, shipped only)</t>
         </is>
       </c>
       <c r="D44" s="44">
         <f>IFERROR(1-AVERAGE(R11:R35)/AVERAGEIF(R11:R35,"&gt;0",J11:J35),"")</f>
         <v/>
       </c>
+      <c r="E44" s="63" t="inlineStr">
+        <is>
+          <t>Average New RPN against average original RPN, over the rows that have a New score. RE-SCORE ONLY WHAT HAS SHIPPED. A control that is built, signed off or awaiting release has not changed the failure rate a customer meets, so leave the row at its original scores until it is live — an FMEA that books the improvement at design time reports a risk reduction the process has not had. Re-score on evidence, the way the benefit is validated at closure.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="52" t="inlineStr">
@@ -3053,8 +3071,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A42:C42"/>
+    <mergeCell ref="E44:Y44"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A44:C44"/>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -3146,10 +3146,10 @@
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="19.5" customHeight="1" s="25">
-      <c r="A4" s="33" t="inlineStr">
-        <is>
-          <t>SEVERITY — how badly does this hurt the customer?</t>
+    <row r="4" ht="48" customHeight="1" s="25">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>SEVERITY — how badly does this hurt the customer?  ·  Key: Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>
       </c>
     </row>
@@ -3250,10 +3250,10 @@
       <c r="F10" s="49" t="n"/>
     </row>
     <row r="11"/>
-    <row r="12" ht="19.5" customHeight="1" s="25">
-      <c r="A12" s="33" t="inlineStr">
-        <is>
-          <t>OCCURRENCE — how often does it happen?</t>
+    <row r="12" ht="48" customHeight="1" s="25">
+      <c r="A12" s="59" t="inlineStr">
+        <is>
+          <t>OCCURRENCE — how often does it happen?  ·  Key: Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>
       </c>
     </row>
@@ -3354,10 +3354,10 @@
       <c r="F18" s="49" t="n"/>
     </row>
     <row r="19"/>
-    <row r="20" ht="19.5" customHeight="1" s="25">
-      <c r="A20" s="33" t="inlineStr">
-        <is>
-          <t>DETECTION — would we catch it before the customer does?  (10 = we would not)</t>
+    <row r="20" ht="48" customHeight="1" s="25">
+      <c r="A20" s="59" t="inlineStr">
+        <is>
+          <t>DETECTION — would we catch it before the customer does?  (10 = we would not)  ·  Key: Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>
       </c>
     </row>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -1159,10 +1159,24 @@
       </c>
     </row>
     <row r="8"/>
-    <row r="9" ht="276" customHeight="1" s="25">
+    <row r="9" ht="624" customHeight="1" s="25">
       <c r="A9" s="59" t="inlineStr">
         <is>
-          <t>SCORE EACH FAILURE MODE 1–10 ON SEVERITY, OCCURRENCE AND DETECTION. THE SCORING GUIDE IS ON THE NEXT SHEET.  ·  Key: Effect on the customer = what the person on the other end experiences, in their words, which is what SEV is scored against. 'Customer discovers it themselves and contacts us again' scores 7; 'margin leakage, caught in reconciliation' scores 4, because the customer never feels it (C11, C15) · SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says · OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see · Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should · DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve · RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks · New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%</t>
+          <t>SCORE EACH FAILURE MODE 1–10 ON SEVERITY, OCCURRENCE AND DETECTION. THE SCORING GUIDE IS ON THE NEXT SHEET.  ·  Key:
+• Effect on the customer = what the person on the other end experiences, in their words, which is what SEV is scored against. 'Customer discovers it themselves and contacts us again' scores 7; 'margin leakage, caught in reconciliation' scores 4, because the customer never feels it (C11, C15)
+• SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says
+• OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see
+• Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should
+• DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve
+• RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks
+• New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%  ·  Key:
+• Effect on the customer = what the person on the other end experiences, in their words, which is what SEV is scored against. 'Customer discovers it themselves and contacts us again' scores 7; 'margin leakage, caught in reconciliation' scores 4, because the customer never feels it (C11, C15)
+• SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says
+• OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see
+• Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should
+• DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve
+• RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks
+• New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%</t>
         </is>
       </c>
     </row>
@@ -3146,10 +3160,12 @@
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="48" customHeight="1" s="25">
+    <row r="4" ht="84" customHeight="1" s="25">
       <c r="A4" s="59" t="inlineStr">
         <is>
-          <t>SEVERITY — how badly does this hurt the customer?  ·  Key: Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
+          <t>SEVERITY — how badly does this hurt the customer?  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>
       </c>
     </row>
@@ -3250,10 +3266,12 @@
       <c r="F10" s="49" t="n"/>
     </row>
     <row r="11"/>
-    <row r="12" ht="48" customHeight="1" s="25">
+    <row r="12" ht="84" customHeight="1" s="25">
       <c r="A12" s="59" t="inlineStr">
         <is>
-          <t>OCCURRENCE — how often does it happen?  ·  Key: Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
+          <t>OCCURRENCE — how often does it happen?  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>
       </c>
     </row>
@@ -3354,10 +3372,12 @@
       <c r="F18" s="49" t="n"/>
     </row>
     <row r="19"/>
-    <row r="20" ht="48" customHeight="1" s="25">
+    <row r="20" ht="84" customHeight="1" s="25">
       <c r="A20" s="59" t="inlineStr">
         <is>
-          <t>DETECTION — would we catch it before the customer does?  (10 = we would not)  ·  Key: Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
+          <t>DETECTION — would we catch it before the customer does?  (10 = we would not)  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>
       </c>
     </row>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -151,6 +151,11 @@
     <font>
       <i val="1"/>
       <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -297,7 +302,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -468,6 +473,9 @@
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -722,7 +730,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>26</col>
+      <col>28</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -1070,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:AI46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="24" min="1" max="1"/>
@@ -1098,6 +1106,15 @@
     <col width="13" customWidth="1" style="25" min="23" max="23"/>
     <col width="13" customWidth="1" style="25" min="24" max="24"/>
     <col width="13" customWidth="1" style="25" min="25" max="25"/>
+    <col width="13" customWidth="1" style="25" min="27" max="27"/>
+    <col width="13" customWidth="1" style="25" min="28" max="28"/>
+    <col width="13" customWidth="1" style="25" min="29" max="29"/>
+    <col width="13" customWidth="1" style="25" min="30" max="30"/>
+    <col width="13" customWidth="1" style="25" min="31" max="31"/>
+    <col width="13" customWidth="1" style="25" min="32" max="32"/>
+    <col width="13" customWidth="1" style="25" min="33" max="33"/>
+    <col width="13" customWidth="1" style="25" min="34" max="34"/>
+    <col width="13" customWidth="1" style="25" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="25">
@@ -1159,7 +1176,7 @@
       </c>
     </row>
     <row r="8"/>
-    <row r="9" ht="624" customHeight="1" s="25">
+    <row r="9" ht="1224" customHeight="1" s="25">
       <c r="A9" s="59" t="inlineStr">
         <is>
           <t>SCORE EACH FAILURE MODE 1–10 ON SEVERITY, OCCURRENCE AND DETECTION. THE SCORING GUIDE IS ON THE NEXT SHEET.  ·  Key:
@@ -1176,6 +1193,20 @@
 • Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should
 • DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve
 • RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks
+• New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%  ·  Key:
+• Effect on the customer = what the person on the other end experiences, in their words, which is what SEV is scored against. 'Customer discovers it themselves and contacts us again' scores 7; 'margin leakage, caught in reconciliation' scores 4, because the customer never feels it (C11, C15)
+• SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says
+• OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see
+• Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should
+• DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve
+• RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks
+• New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%  ·  Key:
+• Effect on the customer = what the person on the other end experiences, in their words, which is what SEV is scored against. 'Customer discovers it themselves and contacts us again' scores 7; 'margin leakage, caught in reconciliation' scores 4, because the customer never feels it (C11, C15)
+• SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says
+• OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see
+• Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should
+• DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve
+• RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks
 • New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%</t>
         </is>
       </c>
@@ -2732,7 +2763,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1" s="25">
+    <row r="32" ht="77" customHeight="1" s="25">
       <c r="A32" s="40" t="n"/>
       <c r="B32" s="40" t="n"/>
       <c r="C32" s="40" t="n"/>
@@ -2783,6 +2814,12 @@
       <c r="Y32" s="53">
         <f>IF(W32="","",$D$45)</f>
         <v/>
+      </c>
+      <c r="AA32" s="64" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Before and after, ranked by the before. Two things to check. A row where the bars are the same height has an action that has not shipped yet — the New scores are only filled once a control is live, so an unchanged pair is honest rather than a failure. And severity 9 or 10 is acted on wherever it ranks, because severity is the one score an action cannot lower.
+SO:  Work the tall before-bars, and act on every severity 9 or 10 wherever it ranks. A pair of equal bars means the action has not shipped — chase the owner and the date, and do not re-score it until the control is live.</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="25">
@@ -3085,7 +3122,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="E44:Y44"/>
     <mergeCell ref="A41:C41"/>
@@ -3096,6 +3133,7 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A46:R46"/>
+    <mergeCell ref="AA32:AI32"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A9:R9"/>
@@ -3160,10 +3198,12 @@
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="84" customHeight="1" s="25">
+    <row r="4" ht="156" customHeight="1" s="25">
       <c r="A4" s="59" t="inlineStr">
         <is>
           <t>SEVERITY — how badly does this hurt the customer?  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
 • Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
 • Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>
@@ -3266,10 +3306,12 @@
       <c r="F10" s="49" t="n"/>
     </row>
     <row r="11"/>
-    <row r="12" ht="84" customHeight="1" s="25">
+    <row r="12" ht="156" customHeight="1" s="25">
       <c r="A12" s="59" t="inlineStr">
         <is>
           <t>OCCURRENCE — how often does it happen?  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
 • Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
 • Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>
@@ -3372,10 +3414,12 @@
       <c r="F18" s="49" t="n"/>
     </row>
     <row r="19"/>
-    <row r="20" ht="84" customHeight="1" s="25">
+    <row r="20" ht="156" customHeight="1" s="25">
       <c r="A20" s="59" t="inlineStr">
         <is>
           <t>DETECTION — would we catch it before the customer does?  (10 = we would not)  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
 • Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
 • Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -1176,31 +1176,10 @@
       </c>
     </row>
     <row r="8"/>
-    <row r="9" ht="1224" customHeight="1" s="25">
+    <row r="9" ht="324" customHeight="1" s="25">
       <c r="A9" s="59" t="inlineStr">
         <is>
           <t>SCORE EACH FAILURE MODE 1–10 ON SEVERITY, OCCURRENCE AND DETECTION. THE SCORING GUIDE IS ON THE NEXT SHEET.  ·  Key:
-• Effect on the customer = what the person on the other end experiences, in their words, which is what SEV is scored against. 'Customer discovers it themselves and contacts us again' scores 7; 'margin leakage, caught in reconciliation' scores 4, because the customer never feels it (C11, C15)
-• SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says
-• OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see
-• Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should
-• DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve
-• RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks
-• New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%  ·  Key:
-• Effect on the customer = what the person on the other end experiences, in their words, which is what SEV is scored against. 'Customer discovers it themselves and contacts us again' scores 7; 'margin leakage, caught in reconciliation' scores 4, because the customer never feels it (C11, C15)
-• SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says
-• OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see
-• Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should
-• DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve
-• RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks
-• New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%  ·  Key:
-• Effect on the customer = what the person on the other end experiences, in their words, which is what SEV is scored against. 'Customer discovers it themselves and contacts us again' scores 7; 'margin leakage, caught in reconciliation' scores 4, because the customer never feels it (C11, C15)
-• SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says
-• OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see
-• Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should
-• DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve
-• RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks
-• New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%  ·  Key:
 • Effect on the customer = what the person on the other end experiences, in their words, which is what SEV is scored against. 'Customer discovers it themselves and contacts us again' scores 7; 'margin leakage, caught in reconciliation' scores 4, because the customer never feels it (C11, C15)
 • SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says
 • OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see
@@ -3198,13 +3177,10 @@
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="156" customHeight="1" s="25">
+    <row r="4" ht="48" customHeight="1" s="25">
       <c r="A4" s="59" t="inlineStr">
         <is>
           <t>SEVERITY — how badly does this hurt the customer?  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
 • Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>
       </c>
@@ -3306,13 +3282,10 @@
       <c r="F10" s="49" t="n"/>
     </row>
     <row r="11"/>
-    <row r="12" ht="156" customHeight="1" s="25">
+    <row r="12" ht="48" customHeight="1" s="25">
       <c r="A12" s="59" t="inlineStr">
         <is>
           <t>OCCURRENCE — how often does it happen?  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
 • Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>
       </c>
@@ -3414,13 +3387,10 @@
       <c r="F18" s="49" t="n"/>
     </row>
     <row r="19"/>
-    <row r="20" ht="156" customHeight="1" s="25">
+    <row r="20" ht="48" customHeight="1" s="25">
       <c r="A20" s="59" t="inlineStr">
         <is>
           <t>DETECTION — would we catch it before the customer does?  (10 = we would not)  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt  ·  Key:
 • Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
         </is>
       </c>

--- a/templates/12-fmea.xlsx
+++ b/templates/12-fmea.xlsx
@@ -302,7 +302,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -476,6 +476,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1045,14 +1048,62 @@
     </row>
     <row r="19"/>
     <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
+    <row r="21" ht="26" customHeight="1" s="25">
+      <c r="A21" s="65" t="inlineStr">
+        <is>
+          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1" s="25">
+      <c r="A22" s="64" t="inlineStr">
+        <is>
+          <t>SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="39" customHeight="1" s="25">
+      <c r="A23" s="64" t="inlineStr">
+        <is>
+          <t>OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="39" customHeight="1" s="25">
+      <c r="A24" s="64" t="inlineStr">
+        <is>
+          <t>Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52" customHeight="1" s="25">
+      <c r="A25" s="64" t="inlineStr">
+        <is>
+          <t>DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1" s="25">
+      <c r="A26" s="64" t="inlineStr">
+        <is>
+          <t>RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="65" customHeight="1" s="25">
+      <c r="A27" s="64" t="inlineStr">
+        <is>
+          <t>New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1" s="25">
+      <c r="A28" s="64" t="inlineStr">
+        <is>
+          <t>Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
+        </is>
+      </c>
+    </row>
     <row r="29"/>
     <row r="30"/>
     <row r="31"/>
@@ -1066,6 +1117,16 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
+  </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1176,17 +1237,17 @@
       </c>
     </row>
     <row r="8"/>
-    <row r="9" ht="324" customHeight="1" s="25">
+    <row r="9" ht="204" customHeight="1" s="25">
       <c r="A9" s="59" t="inlineStr">
         <is>
           <t>SCORE EACH FAILURE MODE 1–10 ON SEVERITY, OCCURRENCE AND DETECTION. THE SCORING GUIDE IS ON THE NEXT SHEET.  ·  Key:
 • Effect on the customer = what the person on the other end experiences, in their words, which is what SEV is scored against. 'Customer discovers it themselves and contacts us again' scores 7; 'margin leakage, caught in reconciliation' scores 4, because the customer never feels it (C11, C15)
-• SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it. It is the one score an action cannot lower: you can stop the batch failing, but if it fails the customer is still late. The batch-failure row scores 8 and stays 8 after the fix (D14, O14). Anything at 9 or 10 is acted on whatever its RPN says
-• OCC = occurrence, 1-10, how often the cause actually happens. This is the score a prevention control moves. Alerting on the nightly batch took its row from 4 to 2 (F14, P14) because the cause stopped recurring, not because it became easier to see
-• Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13). Write what actually happens now, not what the process document says should
-• DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you. The deferred-close row scored 9 — 'only detected if the customer complains again' — and fell to 3 once the webhook confirmed the posting (I11, Q11). In support this column is usually the worst of the three, and the cheapest to improve
-• RPN = risk priority number, severity x occurrence x detection, so 1 to 1000. It is a sorting tool, not a measurement: 504 against 336 says look at the first one first (J11, J16) and nothing more. Two rows can share an RPN with completely different shapes, which is why severity 9 or 10 is acted on regardless of where it ranks
-• New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7. Re-scoring at design time reported a 77.3% risk reduction where the shipped evidence supports 57.7%</t>
+• SEV = severity, 1-10, how badly the CUSTOMER is hurt when this failure happens — not how often, and not how likely you are to catch it.
+• OCC = occurrence, 1-10, how often the cause actually happens.
+• Detection control = what would catch this failure if it happened today, and how late. 'Only detected if the customer complains again' scores DET 9; 'detected immediately on bounce-back' scores 3 (H11, H13).
+• DET = detection, 1-10, and the scale runs BACKWARDS: 1 means you catch it before the customer does, 10 means the customer tells you.
+• RPN = risk priority number, severity x occurrence x detection, so 1 to 1000.
+• New SEV / New OCC / New DET = the same three scores AFTER the action, and only once it has SHIPPED. A control that is built, signed off or awaiting release has not changed what a customer meets, so the row keeps its original scores until it is live — the 'pending release' row sits at 6 / 9 / 8, unchanged, and the 'in backlog' row at 4 / 6 / 7.</t>
         </is>
       </c>
     </row>
@@ -3177,11 +3238,11 @@
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="48" customHeight="1" s="25">
+    <row r="4" ht="36" customHeight="1" s="25">
       <c r="A4" s="59" t="inlineStr">
         <is>
           <t>SEVERITY — how badly does this hurt the customer?  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place.</t>
         </is>
       </c>
     </row>
@@ -3282,11 +3343,11 @@
       <c r="F10" s="49" t="n"/>
     </row>
     <row r="11"/>
-    <row r="12" ht="48" customHeight="1" s="25">
+    <row r="12" ht="36" customHeight="1" s="25">
       <c r="A12" s="59" t="inlineStr">
         <is>
           <t>OCCURRENCE — how often does it happen?  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place.</t>
         </is>
       </c>
     </row>
@@ -3387,11 +3448,11 @@
       <c r="F18" s="49" t="n"/>
     </row>
     <row r="19"/>
-    <row r="20" ht="48" customHeight="1" s="25">
+    <row r="20" ht="36" customHeight="1" s="25">
       <c r="A20" s="59" t="inlineStr">
         <is>
           <t>DETECTION — would we catch it before the customer does?  (10 = we would not)  ·  Key:
-• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place. Severity runs from 1-2 'the customer does not notice' to 9-10 'regulatory breach, safety issue, data exposure or mass impact'. Score against the anchor, not against how the last one felt</t>
+• Score = the 1-10 anchor band, written out so two people scoring the same failure mode land in the same place.</t>
         </is>
       </c>
     </row>
